--- a/MASST_Dataset.xlsx
+++ b/MASST_Dataset.xlsx
@@ -100,13 +100,13 @@
     <t>V27_RationingNecessary</t>
   </si>
   <si>
-    <t>V28_ConservingSavesMonney</t>
+    <t>V28_ConservingSavesMoney</t>
   </si>
   <si>
     <t>V29_NaturalGasDoneEnough</t>
   </si>
   <si>
-    <t>V30_BillSameNomatter</t>
+    <t>V30_BillSameNoMatter</t>
   </si>
   <si>
     <t>V31_CitizenCannotHelp</t>
